--- a/artfynd/A 1879-2024 artfynd.xlsx
+++ b/artfynd/A 1879-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116102166</v>
+        <v>115967074</v>
       </c>
       <c r="B2" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +704,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>806062</v>
+        <v>806271</v>
       </c>
       <c r="R2" t="n">
-        <v>7363708</v>
+        <v>7363562</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +764,21 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,51 +795,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116101687</v>
+        <v>116101662</v>
       </c>
       <c r="B3" t="n">
-        <v>55873</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>806223</v>
+        <v>806228</v>
       </c>
       <c r="R3" t="n">
-        <v>7363766</v>
+        <v>7363624</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116102322</v>
+        <v>116101825</v>
       </c>
       <c r="B4" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>806046</v>
+        <v>806078</v>
       </c>
       <c r="R4" t="n">
-        <v>7363742</v>
+        <v>7363704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,37 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116102396</v>
+        <v>116102133</v>
       </c>
       <c r="B5" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>806035</v>
+        <v>806073</v>
       </c>
       <c r="R5" t="n">
-        <v>7363762</v>
+        <v>7363714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,15 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116102464</v>
+        <v>116102166</v>
       </c>
       <c r="B6" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>806002</v>
+        <v>806062</v>
       </c>
       <c r="R6" t="n">
-        <v>7363771</v>
+        <v>7363708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,12 +1202,7 @@
         <v>116102244</v>
       </c>
       <c r="B7" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,15 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116102480</v>
+        <v>116102322</v>
       </c>
       <c r="B8" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>805991</v>
+        <v>806046</v>
       </c>
       <c r="R8" t="n">
-        <v>7363777</v>
+        <v>7363742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,15 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116102133</v>
+        <v>116102387</v>
       </c>
       <c r="B9" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1429,11 @@
           <t>(L.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1468,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>806073</v>
+        <v>806045</v>
       </c>
       <c r="R9" t="n">
-        <v>7363714</v>
+        <v>7363747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,6 +1481,11 @@
           <t>2024-03-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1515,6 +1495,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1531,37 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116102512</v>
+        <v>116102464</v>
       </c>
       <c r="B10" t="n">
-        <v>79655</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>637</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>805961</v>
+        <v>806002</v>
       </c>
       <c r="R10" t="n">
-        <v>7363798</v>
+        <v>7363771</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,37 +1627,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116102487</v>
+        <v>116102480</v>
       </c>
       <c r="B11" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>805961</v>
+        <v>805991</v>
       </c>
       <c r="R11" t="n">
-        <v>7363798</v>
+        <v>7363777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,15 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116101825</v>
+        <v>116101512</v>
       </c>
       <c r="B12" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,21 +1739,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>806078</v>
+        <v>806244</v>
       </c>
       <c r="R12" t="n">
-        <v>7363704</v>
+        <v>7363613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,15 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116102387</v>
+        <v>116101815</v>
       </c>
       <c r="B13" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,28 +1840,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1896,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>806045</v>
+        <v>806096</v>
       </c>
       <c r="R13" t="n">
-        <v>7363747</v>
+        <v>7363668</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,11 +1905,6 @@
           <t>2024-03-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1949,21 +1915,6 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -1976,6 +1927,418 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>116102396</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mörtträskbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>806035</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7363762</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>116102487</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörtträskbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>805961</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7363798</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>116102512</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mörtträskbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>805961</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7363798</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>116101687</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörtträskbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>806223</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7363766</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1879-2024 artfynd.xlsx
+++ b/artfynd/A 1879-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115967074</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116101662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116101825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102133</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102166</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102244</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102322</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102387</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102464</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102480</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,6 +1881,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116101512</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1927,6 +1987,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116101815</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2028,6 +2093,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102396</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2129,6 +2199,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102487</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2230,6 +2305,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116102512</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2339,8 +2419,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116101687</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>